--- a/docs/dataset/RADAR_Test_RQ.xlsx
+++ b/docs/dataset/RADAR_Test_RQ.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="RQ Input" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RQ Input" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,8 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -48,9 +49,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -416,16 +418,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N202"/>
+  <dimension ref="A1:N222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr"/>
-      <c r="B1" t="inlineStr"/>
-      <c r="C1" t="inlineStr"/>
-      <c r="D1" t="inlineStr"/>
-      <c r="E1" t="inlineStr"/>
-      <c r="F1" t="inlineStr"/>
       <c r="G1" t="inlineStr">
         <is>
           <t>ng/L</t>
@@ -11337,6 +11333,1086 @@
       </c>
       <c r="N202" t="n">
         <v>70.43300000000001</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>RQ-Site1-20240105</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Site 1</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="n">
+        <v>45296</v>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Environmental</t>
+        </is>
+      </c>
+      <c r="G203" t="n">
+        <v>487.33</v>
+      </c>
+      <c r="H203" t="n">
+        <v>362.424</v>
+      </c>
+      <c r="I203" t="n">
+        <v>295.385</v>
+      </c>
+      <c r="J203" t="n">
+        <v>361.914</v>
+      </c>
+      <c r="K203" t="n">
+        <v>463.561</v>
+      </c>
+      <c r="L203" t="n">
+        <v>50.125</v>
+      </c>
+      <c r="M203" t="n">
+        <v>24.668</v>
+      </c>
+      <c r="N203" t="n">
+        <v>396.141</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>RQ-Site1-20240210</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Site 1</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="n">
+        <v>45332</v>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Environmental</t>
+        </is>
+      </c>
+      <c r="G204" t="n">
+        <v>426.594</v>
+      </c>
+      <c r="H204" t="n">
+        <v>329.589</v>
+      </c>
+      <c r="I204" t="n">
+        <v>228.718</v>
+      </c>
+      <c r="J204" t="n">
+        <v>134.319</v>
+      </c>
+      <c r="K204" t="n">
+        <v>492.096</v>
+      </c>
+      <c r="L204" t="n">
+        <v>352.848</v>
+      </c>
+      <c r="M204" t="n">
+        <v>493.036</v>
+      </c>
+      <c r="N204" t="n">
+        <v>330.564</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>RQ-Site1-20240317</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Site 1</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="n">
+        <v>45368</v>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Environmental</t>
+        </is>
+      </c>
+      <c r="G205" t="n">
+        <v>427.441</v>
+      </c>
+      <c r="H205" t="n">
+        <v>116.063</v>
+      </c>
+      <c r="I205" t="n">
+        <v>361.121</v>
+      </c>
+      <c r="J205" t="n">
+        <v>49.002</v>
+      </c>
+      <c r="K205" t="n">
+        <v>164.178</v>
+      </c>
+      <c r="L205" t="n">
+        <v>224.79</v>
+      </c>
+      <c r="M205" t="n">
+        <v>262.138</v>
+      </c>
+      <c r="N205" t="n">
+        <v>496.732</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>RQ-Site1-20240422</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Site 1</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="n">
+        <v>45404</v>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Environmental</t>
+        </is>
+      </c>
+      <c r="G206" t="n">
+        <v>315.351</v>
+      </c>
+      <c r="H206" t="n">
+        <v>54.655</v>
+      </c>
+      <c r="I206" t="n">
+        <v>399.087</v>
+      </c>
+      <c r="J206" t="n">
+        <v>380.106</v>
+      </c>
+      <c r="K206" t="n">
+        <v>415.112</v>
+      </c>
+      <c r="L206" t="n">
+        <v>467.466</v>
+      </c>
+      <c r="M206" t="n">
+        <v>390.9</v>
+      </c>
+      <c r="N206" t="n">
+        <v>259.314</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>RQ-Site1-20240528</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Site 1</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="n">
+        <v>45440</v>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Environmental</t>
+        </is>
+      </c>
+      <c r="G207" t="n">
+        <v>332.876</v>
+      </c>
+      <c r="H207" t="n">
+        <v>28.462</v>
+      </c>
+      <c r="I207" t="n">
+        <v>187.809</v>
+      </c>
+      <c r="J207" t="n">
+        <v>204.676</v>
+      </c>
+      <c r="K207" t="n">
+        <v>368.521</v>
+      </c>
+      <c r="L207" t="n">
+        <v>31.746</v>
+      </c>
+      <c r="M207" t="n">
+        <v>103.577</v>
+      </c>
+      <c r="N207" t="n">
+        <v>121.055</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>RQ-Site1-20240703</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Site 1</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>July</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="n">
+        <v>45476</v>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Environmental</t>
+        </is>
+      </c>
+      <c r="G208" t="n">
+        <v>101.08</v>
+      </c>
+      <c r="H208" t="n">
+        <v>236.9</v>
+      </c>
+      <c r="I208" t="n">
+        <v>496.942</v>
+      </c>
+      <c r="J208" t="n">
+        <v>164.875</v>
+      </c>
+      <c r="K208" t="n">
+        <v>34.865</v>
+      </c>
+      <c r="L208" t="n">
+        <v>9.726000000000001</v>
+      </c>
+      <c r="M208" t="n">
+        <v>373.08</v>
+      </c>
+      <c r="N208" t="n">
+        <v>197.589</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>RQ-Site1-20240808</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Site 1</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>August</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="n">
+        <v>45512</v>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Environmental</t>
+        </is>
+      </c>
+      <c r="G209" t="n">
+        <v>493.529</v>
+      </c>
+      <c r="H209" t="n">
+        <v>125.226</v>
+      </c>
+      <c r="I209" t="n">
+        <v>486.757</v>
+      </c>
+      <c r="J209" t="n">
+        <v>156.882</v>
+      </c>
+      <c r="K209" t="n">
+        <v>488.779</v>
+      </c>
+      <c r="L209" t="n">
+        <v>466.222</v>
+      </c>
+      <c r="M209" t="n">
+        <v>200.741</v>
+      </c>
+      <c r="N209" t="n">
+        <v>45.569</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>RQ-Site1-20240913</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Site 1</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="n">
+        <v>45548</v>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Environmental</t>
+        </is>
+      </c>
+      <c r="G210" t="n">
+        <v>310.789</v>
+      </c>
+      <c r="H210" t="n">
+        <v>293.271</v>
+      </c>
+      <c r="I210" t="n">
+        <v>318.682</v>
+      </c>
+      <c r="J210" t="n">
+        <v>72.36</v>
+      </c>
+      <c r="K210" t="n">
+        <v>419.373</v>
+      </c>
+      <c r="L210" t="n">
+        <v>172.936</v>
+      </c>
+      <c r="M210" t="n">
+        <v>159.417</v>
+      </c>
+      <c r="N210" t="n">
+        <v>38.421</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>RQ-Site1-20241019</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Site 1</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>October</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="n">
+        <v>45584</v>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Environmental</t>
+        </is>
+      </c>
+      <c r="G211" t="n">
+        <v>11.61</v>
+      </c>
+      <c r="H211" t="n">
+        <v>224.975</v>
+      </c>
+      <c r="I211" t="n">
+        <v>67.485</v>
+      </c>
+      <c r="J211" t="n">
+        <v>154.799</v>
+      </c>
+      <c r="K211" t="n">
+        <v>369.059</v>
+      </c>
+      <c r="L211" t="n">
+        <v>377.451</v>
+      </c>
+      <c r="M211" t="n">
+        <v>223.243</v>
+      </c>
+      <c r="N211" t="n">
+        <v>113.026</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>RQ-Site1-20241124</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Site 1</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>November</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="n">
+        <v>45620</v>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Environmental</t>
+        </is>
+      </c>
+      <c r="G212" t="n">
+        <v>314.069</v>
+      </c>
+      <c r="H212" t="n">
+        <v>193.054</v>
+      </c>
+      <c r="I212" t="n">
+        <v>492.38</v>
+      </c>
+      <c r="J212" t="n">
+        <v>382.988</v>
+      </c>
+      <c r="K212" t="n">
+        <v>429.115</v>
+      </c>
+      <c r="L212" t="n">
+        <v>136.175</v>
+      </c>
+      <c r="M212" t="n">
+        <v>383.718</v>
+      </c>
+      <c r="N212" t="n">
+        <v>212.181</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>RQ-Site2-20240123</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Site 2</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="n">
+        <v>45314</v>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Environmental</t>
+        </is>
+      </c>
+      <c r="G213" t="n">
+        <v>127.717</v>
+      </c>
+      <c r="H213" t="n">
+        <v>59.069</v>
+      </c>
+      <c r="I213" t="n">
+        <v>256.458</v>
+      </c>
+      <c r="J213" t="n">
+        <v>324.872</v>
+      </c>
+      <c r="K213" t="n">
+        <v>128.569</v>
+      </c>
+      <c r="L213" t="n">
+        <v>48.944</v>
+      </c>
+      <c r="M213" t="n">
+        <v>294.073</v>
+      </c>
+      <c r="N213" t="n">
+        <v>264.314</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>RQ-Site2-20240228</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Site 2</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="n">
+        <v>45350</v>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Environmental</t>
+        </is>
+      </c>
+      <c r="G214" t="n">
+        <v>361.5</v>
+      </c>
+      <c r="H214" t="n">
+        <v>433.314</v>
+      </c>
+      <c r="I214" t="n">
+        <v>84.11499999999999</v>
+      </c>
+      <c r="J214" t="n">
+        <v>486.65</v>
+      </c>
+      <c r="K214" t="n">
+        <v>145.606</v>
+      </c>
+      <c r="L214" t="n">
+        <v>371.997</v>
+      </c>
+      <c r="M214" t="n">
+        <v>118.079</v>
+      </c>
+      <c r="N214" t="n">
+        <v>380.316</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>RQ-Site2-20240404</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Site 2</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="n">
+        <v>45386</v>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Environmental</t>
+        </is>
+      </c>
+      <c r="G215" t="n">
+        <v>176.292</v>
+      </c>
+      <c r="H215" t="n">
+        <v>262.205</v>
+      </c>
+      <c r="I215" t="n">
+        <v>440.338</v>
+      </c>
+      <c r="J215" t="n">
+        <v>382.167</v>
+      </c>
+      <c r="K215" t="n">
+        <v>379.886</v>
+      </c>
+      <c r="L215" t="n">
+        <v>458.22</v>
+      </c>
+      <c r="M215" t="n">
+        <v>205.819</v>
+      </c>
+      <c r="N215" t="n">
+        <v>126.134</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>RQ-Site2-20240510</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Site 2</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="n">
+        <v>45422</v>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Environmental</t>
+        </is>
+      </c>
+      <c r="G216" t="n">
+        <v>414.368</v>
+      </c>
+      <c r="H216" t="n">
+        <v>292.124</v>
+      </c>
+      <c r="I216" t="n">
+        <v>136.771</v>
+      </c>
+      <c r="J216" t="n">
+        <v>491.078</v>
+      </c>
+      <c r="K216" t="n">
+        <v>447.245</v>
+      </c>
+      <c r="L216" t="n">
+        <v>400.15</v>
+      </c>
+      <c r="M216" t="n">
+        <v>231.021</v>
+      </c>
+      <c r="N216" t="n">
+        <v>402.312</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>RQ-Site2-20240615</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Site 2</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>June</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="n">
+        <v>45458</v>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Environmental</t>
+        </is>
+      </c>
+      <c r="G217" t="n">
+        <v>199.719</v>
+      </c>
+      <c r="H217" t="n">
+        <v>145.493</v>
+      </c>
+      <c r="I217" t="n">
+        <v>407.71</v>
+      </c>
+      <c r="J217" t="n">
+        <v>303.618</v>
+      </c>
+      <c r="K217" t="n">
+        <v>371.482</v>
+      </c>
+      <c r="L217" t="n">
+        <v>38.735</v>
+      </c>
+      <c r="M217" t="n">
+        <v>262.041</v>
+      </c>
+      <c r="N217" t="n">
+        <v>209.393</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>RQ-Site2-20240721</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Site 2</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>July</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="n">
+        <v>45494</v>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Environmental</t>
+        </is>
+      </c>
+      <c r="G218" t="n">
+        <v>21.249</v>
+      </c>
+      <c r="H218" t="n">
+        <v>422.337</v>
+      </c>
+      <c r="I218" t="n">
+        <v>227.025</v>
+      </c>
+      <c r="J218" t="n">
+        <v>240.19</v>
+      </c>
+      <c r="K218" t="n">
+        <v>289.385</v>
+      </c>
+      <c r="L218" t="n">
+        <v>311.086</v>
+      </c>
+      <c r="M218" t="n">
+        <v>62.409</v>
+      </c>
+      <c r="N218" t="n">
+        <v>100.229</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>RQ-Site2-20240826</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Site 2</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>August</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="n">
+        <v>45530</v>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Environmental</t>
+        </is>
+      </c>
+      <c r="G219" t="n">
+        <v>49.912</v>
+      </c>
+      <c r="H219" t="n">
+        <v>319.381</v>
+      </c>
+      <c r="I219" t="n">
+        <v>85.712</v>
+      </c>
+      <c r="J219" t="n">
+        <v>347.552</v>
+      </c>
+      <c r="K219" t="n">
+        <v>395.608</v>
+      </c>
+      <c r="L219" t="n">
+        <v>374.378</v>
+      </c>
+      <c r="M219" t="n">
+        <v>491.092</v>
+      </c>
+      <c r="N219" t="n">
+        <v>259.651</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>RQ-Site2-20241001</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Site 2</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>October</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="n">
+        <v>45566</v>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Environmental</t>
+        </is>
+      </c>
+      <c r="G220" t="n">
+        <v>269.712</v>
+      </c>
+      <c r="H220" t="n">
+        <v>289.45</v>
+      </c>
+      <c r="I220" t="n">
+        <v>302.437</v>
+      </c>
+      <c r="J220" t="n">
+        <v>260.303</v>
+      </c>
+      <c r="K220" t="n">
+        <v>130.253</v>
+      </c>
+      <c r="L220" t="n">
+        <v>351.305</v>
+      </c>
+      <c r="M220" t="n">
+        <v>382.162</v>
+      </c>
+      <c r="N220" t="n">
+        <v>173.757</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>RQ-Site2-20241106</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Site 2</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>November</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="n">
+        <v>45602</v>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Environmental</t>
+        </is>
+      </c>
+      <c r="G221" t="n">
+        <v>50.557</v>
+      </c>
+      <c r="H221" t="n">
+        <v>293.393</v>
+      </c>
+      <c r="I221" t="n">
+        <v>124.722</v>
+      </c>
+      <c r="J221" t="n">
+        <v>164.176</v>
+      </c>
+      <c r="K221" t="n">
+        <v>438.184</v>
+      </c>
+      <c r="L221" t="n">
+        <v>397.558</v>
+      </c>
+      <c r="M221" t="n">
+        <v>476.838</v>
+      </c>
+      <c r="N221" t="n">
+        <v>291.669</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>RQ-Site2-20241212</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Site 2</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>December</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="n">
+        <v>45638</v>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Environmental</t>
+        </is>
+      </c>
+      <c r="G222" t="n">
+        <v>362.829</v>
+      </c>
+      <c r="H222" t="n">
+        <v>124.487</v>
+      </c>
+      <c r="I222" t="n">
+        <v>312.99</v>
+      </c>
+      <c r="J222" t="n">
+        <v>275.343</v>
+      </c>
+      <c r="K222" t="n">
+        <v>101.091</v>
+      </c>
+      <c r="L222" t="n">
+        <v>318.89</v>
+      </c>
+      <c r="M222" t="n">
+        <v>319.309</v>
+      </c>
+      <c r="N222" t="n">
+        <v>91.688</v>
       </c>
     </row>
   </sheetData>
